--- a/tests/testthat/golden/puttab.xlsx
+++ b/tests/testthat/golden/puttab.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="28">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -407,27 +407,37 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <i/>
+      <sz val="8"/>
       <name val="Arial"/>
-      <b/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
+      <sz val="14"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="10"/>
-      <b/>
+      <i/>
+      <sz val="6"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -435,97 +445,22 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <i/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <b/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <i/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <i/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="8"/>
+      <i/>
+      <sz val="6"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Times New Roman"/>
       <b/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <b/>
+      <sz val="6"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="Times New Roman"/>
       <b/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <b/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="Times New Roman"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <i/>
+      <sz val="8"/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -539,30 +474,35 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBE5F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF0C8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE6C8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC8C8C8"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -572,352 +512,349 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium"/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -945,247 +882,247 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="10" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="14" t="s">
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="8" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1209,70 +1146,70 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="18" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="6" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="8" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1294,68 +1231,68 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="64" t="s">
+      <c r="A1" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="61" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="69" t="s">
+      <c r="A2" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="59" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="61" t="s">
+      <c r="A3" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="56" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="61" t="s">
+      <c r="A4" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="56" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="71" t="s">
+      <c r="A5" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="55" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="57" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="61" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="74" t="s">
+      <c r="A6" s="53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="58" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1378,46 +1315,46 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1438,50 +1375,50 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="66" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="64" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="64" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="62" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1505,87 +1442,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="16" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="23" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="23" t="s">
+      <c r="C5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1610,87 +1547,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="8" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1714,87 +1651,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="30" t="s">
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="31" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="31" t="s">
+      <c r="A2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="28" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="36" t="s">
+      <c r="A3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="30" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="34" t="s">
+      <c r="A4" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="26" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="40" t="s">
+      <c r="A5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="40" t="s">
+      <c r="C5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1820,122 +1757,122 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="41" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="39" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="35" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="E6" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="37" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1960,39 +1897,39 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="52" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="49" t="s">
+      <c r="B1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="50" t="s">
+      <c r="A2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="51" t="s">
+      <c r="D2" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="51" t="s">
+      <c r="E2" s="50" t="s">
         <v>88</v>
       </c>
       <c r="F2" s="51" t="s">
@@ -2000,62 +1937,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="52" t="s">
+      <c r="C3" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="52" t="s">
+      <c r="E3" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="52" t="s">
+      <c r="F3" s="47" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="54" t="s">
+      <c r="A4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="E4" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="54" t="s">
+      <c r="E4" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="49" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="57" t="s">
+      <c r="A5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="57" t="s">
+      <c r="C5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="41" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2078,46 +2015,46 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="18" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="8" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2138,58 +2075,58 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2211,35 +2148,35 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="18" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="8" t="s">
         <v>71</v>
       </c>
     </row>
